--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/abr-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/abr-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M267"/>
+  <dimension ref="A1:M261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>14082936</v>
+        <v>15684.54</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>314064.8</v>
+        <v>349.78</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>15157625</v>
+        <v>16881.45</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>601132.0699999999</v>
+        <v>669.5</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>462474.46</v>
+        <v>515.0700000000001</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7901181.12</v>
+        <v>8799.76</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>215190.08</v>
+        <v>239.66</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1475345.34</v>
+        <v>1643.13</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>607809.16</v>
+        <v>676.9299999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7550642.82</v>
+        <v>8409.35</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>910734.37</v>
+        <v>1014.31</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8197742.21</v>
+        <v>9130.049999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12598184.9</v>
+        <v>14030.94</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>613449.76</v>
+        <v>683.22</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>132310.15</v>
+        <v>147.36</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>240827.44</v>
+        <v>268.22</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1794229.64</v>
+        <v>1998.28</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>22357321.35</v>
+        <v>24899.95</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8366772.19</v>
+        <v>9318.299999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>36610112</v>
+        <v>40773.67</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>45174542</v>
+        <v>50312.1</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8272659.85</v>
+        <v>9213.48</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>94138.52</v>
+        <v>104.84</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7615583.5</v>
+        <v>8481.68</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>52877107.36</v>
+        <v>58890.66</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1095742.48</v>
+        <v>1220.36</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>839359.36</v>
+        <v>934.8200000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7785597.61</v>
+        <v>8671.030000000001</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5830452.6</v>
+        <v>6493.53</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>598988.88</v>
+        <v>667.11</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7936.75</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>466959.57</v>
+        <v>520.0700000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>548347.24</v>
+        <v>610.71</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2423430.24</v>
+        <v>2699.04</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>583596.23</v>
+        <v>649.97</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>15114508.92</v>
+        <v>16833.43</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>494683</v>
+        <v>550.9400000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>417404.4</v>
+        <v>464.87</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4177333.16</v>
+        <v>4652.41</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7936.75</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1000944.7</v>
+        <v>1114.78</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>383259.73</v>
+        <v>426.85</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3905401.5</v>
+        <v>4349.55</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>988969.73</v>
+        <v>1101.44</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2248683.5</v>
+        <v>2504.42</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>588641.83</v>
+        <v>655.59</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7936.75</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7936.75</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2012278.1</v>
+        <v>2241.13</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>184886.73</v>
+        <v>205.91</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>821633.12</v>
+        <v>915.0700000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>231577.57</v>
+        <v>257.91</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>622101.0600000001</v>
+        <v>692.85</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1749726.02</v>
+        <v>1948.72</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12498808</v>
+        <v>13920.26</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7936.75</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>712314.96</v>
+        <v>793.3200000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4225,11 +4225,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7127581.16</v>
+        <v>7938.18</v>
       </c>
     </row>
     <row r="63">
@@ -4286,11 +4286,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7197449.63</v>
+        <v>8015.99</v>
       </c>
     </row>
     <row r="64">
@@ -4347,11 +4347,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>7197449.63</v>
+        <v>8015.99</v>
       </c>
     </row>
     <row r="65">
@@ -4408,11 +4408,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4389203.14</v>
+        <v>4888.37</v>
       </c>
     </row>
     <row r="66">
@@ -4469,11 +4469,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>14252594.3</v>
+        <v>15873.5</v>
       </c>
     </row>
     <row r="67">
@@ -4530,11 +4530,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1217079.64</v>
+        <v>1355.49</v>
       </c>
     </row>
     <row r="68">
@@ -4591,11 +4591,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2785433</v>
+        <v>3102.21</v>
       </c>
     </row>
     <row r="69">
@@ -4652,11 +4652,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3252020.1</v>
+        <v>3621.86</v>
       </c>
     </row>
     <row r="70">
@@ -4713,11 +4713,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7602257.88</v>
+        <v>8466.84</v>
       </c>
     </row>
     <row r="71">
@@ -4774,11 +4774,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2991303</v>
+        <v>3331.49</v>
       </c>
     </row>
     <row r="72">
@@ -4835,11 +4835,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>12099920</v>
+        <v>13476.01</v>
       </c>
     </row>
     <row r="73">
@@ -4896,11 +4896,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>497976.92</v>
+        <v>554.61</v>
       </c>
     </row>
     <row r="74">
@@ -4957,11 +4957,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>7954942.94</v>
+        <v>8859.629999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5018,11 +5018,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>10317300</v>
+        <v>11490.65</v>
       </c>
     </row>
     <row r="76">
@@ -5079,11 +5079,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7989983.68</v>
+        <v>8898.66</v>
       </c>
     </row>
     <row r="77">
@@ -5140,11 +5140,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>295747.13</v>
+        <v>329.38</v>
       </c>
     </row>
     <row r="78">
@@ -5201,11 +5201,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7198211.23</v>
+        <v>8016.84</v>
       </c>
     </row>
     <row r="79">
@@ -5262,11 +5262,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>276110.94</v>
+        <v>307.51</v>
       </c>
     </row>
     <row r="80">
@@ -5323,11 +5323,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>24474135</v>
+        <v>27257.5</v>
       </c>
     </row>
     <row r="81">
@@ -5384,11 +5384,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7604124.99</v>
+        <v>8468.92</v>
       </c>
     </row>
     <row r="82">
@@ -5445,11 +5445,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1039202.01</v>
+        <v>1157.39</v>
       </c>
     </row>
     <row r="83">
@@ -5506,11 +5506,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8183058.8</v>
+        <v>9113.690000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5567,11 +5567,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1391945.38</v>
+        <v>1550.25</v>
       </c>
     </row>
     <row r="85">
@@ -5628,11 +5628,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>658274.6800000001</v>
+        <v>733.14</v>
       </c>
     </row>
     <row r="86">
@@ -5689,11 +5689,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>49884080.05</v>
+        <v>55557.24</v>
       </c>
     </row>
     <row r="87">
@@ -5750,17 +5750,17 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3570298.69</v>
+        <v>3976.34</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3567-199-CM26</t>
+          <t>1078078-1095-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5780,17 +5780,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.150.700-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FLORIDA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,28 +5800,28 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3018951.46</v>
+        <v>838.3099999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1078078-1095-CM26</t>
+          <t>1078078-1084-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5861,28 +5861,28 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>752710.7</v>
+        <v>8016.84</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1078078-1084-CM26</t>
+          <t>1078078-1089-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5922,28 +5922,28 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>7198211.23</v>
+        <v>8005.01</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1078078-1089-CM26</t>
+          <t>1078078-1082-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5983,28 +5983,28 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7187588.1</v>
+        <v>932.14</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1078078-1082-CM26</t>
+          <t>1078078-1067-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6044,28 +6044,28 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>836955.5600000001</v>
+        <v>8005.01</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1078078-1067-CM26</t>
+          <t>1078078-1068-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6105,28 +6105,28 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7187588.1</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1078078-1068-CM26</t>
+          <t>1078078-1069-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6166,28 +6166,28 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>103794.18</v>
+        <v>9113.690000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1078078-1069-CM26</t>
+          <t>1078078-1070-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6227,28 +6227,28 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8183058.8</v>
+        <v>670.08</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1078078-1070-CM26</t>
+          <t>1078078-1071-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6299,17 +6299,17 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>601658.05</v>
+        <v>168.23</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1078078-1071-CM26</t>
+          <t>1078078-1072-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6349,28 +6349,28 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>151052.65</v>
+        <v>18473.62</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1078078-1072-CM26</t>
+          <t>1078078-1073-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6410,28 +6410,28 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>16587204.13</v>
+        <v>16937.84</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1078078-1073-CM26</t>
+          <t>1078078-1083-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6471,28 +6471,28 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>15208249.98</v>
+        <v>8005.01</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1078078-1083-CM26</t>
+          <t>1078078-1074-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6532,28 +6532,28 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>7187588.1</v>
+        <v>1412.27</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1078078-1074-CM26</t>
+          <t>1078078-1076-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6604,17 +6604,17 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1268061.62</v>
+        <v>558.16</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1078078-1076-CM26</t>
+          <t>1078078-1077-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6654,28 +6654,28 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>501161.36</v>
+        <v>8412.950000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1078078-1077-CM26</t>
+          <t>1078078-1078-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6715,28 +6715,28 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>7553872.48</v>
+        <v>521.75</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1078078-1078-CM26</t>
+          <t>1079486-48-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6761,43 +6761,43 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>468475.63</v>
+        <v>11496.22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1079486-48-CM26</t>
+          <t>1078078-1079-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6822,43 +6822,43 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10322298</v>
+        <v>8412.950000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1078078-1079-CM26</t>
+          <t>1078078-1080-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6898,28 +6898,28 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>7553872.48</v>
+        <v>821.61</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1078078-1080-CM26</t>
+          <t>1078078-1081-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6959,28 +6959,28 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>737708.37</v>
+        <v>8005.01</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1078078-1081-CM26</t>
+          <t>1078078-1075-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7020,28 +7020,28 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7187588.1</v>
+        <v>8015.99</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1078078-1075-CM26</t>
+          <t>2450-440-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,53 +7056,53 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>7197449.63</v>
+        <v>1456.98</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2450-440-CM26</t>
+          <t>1250355-13-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,43 +7127,43 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.933.800-6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1308205.08</v>
+        <v>20518.77</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1250355-13-CM26</t>
+          <t>2450-424-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7188,43 +7188,43 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.933.800-6</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>18423520.5</v>
+        <v>7819.96</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2450-424-CM26</t>
+          <t>4964-25-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,43 +7249,43 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>7021433.16</v>
+        <v>11327.64</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4964-25-CM26</t>
+          <t>4351-175-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7305,48 +7305,48 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>10170930</v>
+        <v>684.52</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4351-175-CM26</t>
+          <t>3267-53-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7366,48 +7366,48 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>614625.48</v>
+        <v>216.29</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3267-53-CM26</t>
+          <t>2436-416-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7427,48 +7427,48 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>194208</v>
+        <v>37669.97</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2436-416-CM26</t>
+          <t>1079639-291-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7488,48 +7488,48 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>33823346.2</v>
+        <v>6752.37</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1079639-291-CM26</t>
+          <t>2676-225-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7549,48 +7549,48 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6062859.6</v>
+        <v>6821.21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2676-225-CM26</t>
+          <t>1078078-1121-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,22 +7605,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,22 +7630,22 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>6124672.96</v>
+        <v>16835.36</v>
       </c>
     </row>
     <row r="119">
@@ -7702,11 +7702,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1164307.9</v>
+        <v>1296.72</v>
       </c>
     </row>
     <row r="120">
@@ -7763,11 +7763,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>767958.17</v>
+        <v>855.3</v>
       </c>
     </row>
     <row r="121">
@@ -7824,11 +7824,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2395317.68</v>
+        <v>2667.73</v>
       </c>
     </row>
     <row r="122">
@@ -7885,11 +7885,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>7604124.99</v>
+        <v>8468.92</v>
       </c>
     </row>
     <row r="123">
@@ -7946,11 +7946,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>435706.6</v>
+        <v>485.26</v>
       </c>
     </row>
     <row r="124">
@@ -8007,11 +8007,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>601658.05</v>
+        <v>670.08</v>
       </c>
     </row>
     <row r="125">
@@ -8068,11 +8068,11 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1049376.51</v>
+        <v>1168.72</v>
       </c>
     </row>
     <row r="126">
@@ -8129,11 +8129,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>410816.56</v>
+        <v>457.54</v>
       </c>
     </row>
     <row r="127">
@@ -8190,11 +8190,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>7737031.33</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="128">
@@ -8251,11 +8251,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>7737031.33</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="129">
@@ -8312,11 +8312,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>18811723.49</v>
+        <v>20951.12</v>
       </c>
     </row>
     <row r="130">
@@ -8373,11 +8373,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>557708.97</v>
+        <v>621.14</v>
       </c>
     </row>
     <row r="131">
@@ -8434,17 +8434,17 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>261514.4</v>
+        <v>291.26</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1078078-1121-CM26</t>
+          <t>1078078-1120-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8484,28 +8484,28 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>15116241.56</v>
+        <v>668.39</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1078078-1120-CM26</t>
+          <t>1078078-1118-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8545,28 +8545,28 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>600134.85</v>
+        <v>8412.950000000001</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1078078-1105-CM26</t>
+          <t>1078078-1104-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8606,28 +8606,28 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>451578.82</v>
+        <v>626.04</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1078078-1103-CM26</t>
+          <t>1078078-1119-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8667,28 +8667,28 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>7557312.77</v>
+        <v>2148.35</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1078078-1104-CM26</t>
+          <t>1078078-1103-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8739,17 +8739,17 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>562114.35</v>
+        <v>8416.780000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1078078-1108-CM26</t>
+          <t>1078078-1105-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8789,28 +8789,28 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>7553872.48</v>
+        <v>502.94</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1078078-1109-CM26</t>
+          <t>1078078-1108-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8850,28 +8850,28 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>454877.5</v>
+        <v>8412.950000000001</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1078078-1111-CM26</t>
+          <t>1078078-1109-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8922,17 +8922,17 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>669886.7</v>
+        <v>506.61</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1078078-1112-CM26</t>
+          <t>1078078-1111-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8972,22 +8972,22 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1129855.02</v>
+        <v>746.0700000000001</v>
       </c>
     </row>
     <row r="141">
@@ -9044,17 +9044,17 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8416.790000000001</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1078078-1114-CM26</t>
+          <t>1078078-1113-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -9094,28 +9094,28 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1078078-1115-CM26</t>
+          <t>1078078-1114-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -9155,28 +9155,28 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>605781.4</v>
+        <v>8416.790000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1078078-1116-CM26</t>
+          <t>1078078-1115-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9216,28 +9216,28 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>423756.62</v>
+        <v>674.6799999999999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1078078-1117-CM26</t>
+          <t>1078078-1116-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9277,28 +9277,28 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>16366117.6</v>
+        <v>471.95</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1078078-1118-CM26</t>
+          <t>1078078-1117-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9338,28 +9338,28 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>7553872.48</v>
+        <v>18227.39</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1078078-1113-CM26</t>
+          <t>1078078-1112-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9399,28 +9399,28 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>7737028.95</v>
+        <v>1258.35</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1078078-1119-CM26</t>
+          <t>1078078-1150-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9460,28 +9460,28 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1928972.15</v>
+        <v>8690.389999999999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1078078-1151-CM26</t>
+          <t>1078078-1148-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9521,28 +9521,28 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>7785597.61</v>
+        <v>8015.99</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1078078-1148-CM26</t>
+          <t>1078078-1149-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9582,28 +9582,28 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>7197449.63</v>
+        <v>1112.66</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1078078-1149-CM26</t>
+          <t>1078078-1151-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9643,28 +9643,28 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>999043.08</v>
+        <v>8671.030000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1078078-1150-CM26</t>
+          <t>1078078-1146-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9704,28 +9704,28 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>7802984.7</v>
+        <v>3925.58</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1078078-1152-CM26</t>
+          <t>1078078-1153-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9776,11 +9776,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>561327.76</v>
+        <v>703.62</v>
       </c>
     </row>
     <row r="154">
@@ -9837,11 +9837,11 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4520812.38</v>
+        <v>5034.95</v>
       </c>
     </row>
     <row r="155">
@@ -9898,11 +9898,11 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>31959934.72</v>
+        <v>35594.64</v>
       </c>
     </row>
     <row r="156">
@@ -9959,17 +9959,17 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3720892</v>
+        <v>4144.06</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1078078-1153-CM26</t>
+          <t>1078078-1152-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10020,11 +10020,11 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>631771</v>
+        <v>625.17</v>
       </c>
     </row>
     <row r="158">
@@ -10081,17 +10081,17 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>582650.1800000001</v>
+        <v>648.91</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1078078-1146-CM26</t>
+          <t>1078078-1144-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10131,28 +10131,28 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3524720.5</v>
+        <v>8815.629999999999</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1078078-1144-CM26</t>
+          <t>1078078-1136-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10203,17 +10203,17 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>7915436.13</v>
+        <v>592.98</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1078078-1143-CM26</t>
+          <t>2273-163-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10233,17 +10233,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,28 +10253,28 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>FIRAMCO SPA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.942.697-1</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>475151.53</v>
+        <v>9807.48</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1078078-1142-CM26</t>
+          <t>1078078-1143-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10314,28 +10314,28 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>7737028.95</v>
+        <v>529.1900000000001</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1078078-1141-CM26</t>
+          <t>1078078-1142-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10375,28 +10375,28 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>49884080.05</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1078078-1140-CM26</t>
+          <t>1078078-1141-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10436,28 +10436,28 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>475151.53</v>
+        <v>55557.24</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1078078-1138-CM26</t>
+          <t>1078078-1140-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10508,17 +10508,17 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>513574.25</v>
+        <v>529.1900000000001</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1078078-1137-CM26</t>
+          <t>1078078-1138-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10558,28 +10558,28 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>7737028.95</v>
+        <v>571.98</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1078078-1136-CM26</t>
+          <t>1078078-1137-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10630,11 +10630,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>532432.1800000001</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="168">
@@ -10691,17 +10691,17 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>27739710.39</v>
+        <v>30894.46</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2273-163-CM26</t>
+          <t>2765-151-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,28 +10741,28 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>FIRAMCO SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>77.942.697-1</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>8806000</v>
+        <v>5649.11</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2765-151-CM26</t>
+          <t>1079454-109-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10777,27 +10777,27 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10813,11 +10813,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>5072256</v>
+        <v>22980.04</v>
       </c>
     </row>
     <row r="171">
@@ -10874,17 +10874,17 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>419475</v>
+        <v>467.18</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1079454-109-CM26</t>
+          <t>2799-417-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10899,53 +10899,53 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>20633461.17</v>
+        <v>278.17</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1078078-1161-CM26</t>
+          <t>2674-343-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10985,28 +10985,28 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>821690.24</v>
+        <v>1935.52</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1078078-1160-CM26</t>
+          <t>1078078-1158-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11046,22 +11046,22 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>7557254.46</v>
+        <v>933.64</v>
       </c>
     </row>
     <row r="175">
@@ -11118,17 +11118,17 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>358428</v>
+        <v>399.19</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2674-343-CM26</t>
+          <t>1078078-1160-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11148,17 +11148,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11168,28 +11168,28 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1737876</v>
+        <v>8416.719999999999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1078078-1158-CM26</t>
+          <t>1078078-1161-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -11229,28 +11229,28 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>838302.64</v>
+        <v>915.14</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2799-417-CM26</t>
+          <t>1078078-1171-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11275,43 +11275,43 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>249767.91</v>
+        <v>2390.46</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1078078-1159-CM26</t>
+          <t>1078078-1172-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11351,28 +11351,28 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3664709.72</v>
+        <v>17322.6</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1078078-1170-CM26</t>
+          <t>1078078-1173-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11412,22 +11412,22 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7197449.63</v>
+        <v>1929.83</v>
       </c>
     </row>
     <row r="181">
@@ -11484,17 +11484,17 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>574789.04</v>
+        <v>640.16</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1078078-1176-CM26</t>
+          <t>1078078-1175-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -11534,28 +11534,28 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7989983.68</v>
+        <v>561.42</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1079563-151-CM26</t>
+          <t>1078078-1176-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11575,48 +11575,48 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>12557618.99</v>
+        <v>8898.66</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1078078-1174-CM26</t>
+          <t>1078078-1170-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11667,17 +11667,17 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>7197449.63</v>
+        <v>8015.99</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1078078-1173-CM26</t>
+          <t>1078078-1174-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11717,28 +11717,28 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1732763.76</v>
+        <v>8015.99</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1078078-1172-CM26</t>
+          <t>1078078-1169-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11778,28 +11778,28 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>15553721.26</v>
+        <v>5507.32</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1078078-1171-CM26</t>
+          <t>1079563-151-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11824,43 +11824,43 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SECCIÓN COMPRAS VI ZONA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2146360.16</v>
+        <v>13985.76</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1078078-1169-CM26</t>
+          <t>1078078-1167-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11900,28 +11900,28 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4944949.8</v>
+        <v>8015.99</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1078078-1175-CM26</t>
+          <t>2429-375-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11946,43 +11946,43 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>504087.57</v>
+        <v>11395.23</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1078078-1167-CM26</t>
+          <t>1078078-1166-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -12022,28 +12022,28 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>7197449.63</v>
+        <v>411.2</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2429-375-CM26</t>
+          <t>1078078-1165-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12068,43 +12068,43 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>10231620</v>
+        <v>1904.83</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1078078-1166-CM26</t>
+          <t>1078078-1164-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -12144,28 +12144,28 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>369210.59</v>
+        <v>7936.75</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1078078-1165-CM26</t>
+          <t>1078078-1163-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12216,17 +12216,17 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1710322.74</v>
+        <v>173.6</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1078078-1164-CM26</t>
+          <t>1078078-1168-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -12266,28 +12266,28 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>7126297.15</v>
+        <v>940.72</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1078078-1163-CM26</t>
+          <t>1078078-1162-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12338,17 +12338,17 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>155873.34</v>
+        <v>1410.73</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1078078-1162-CM26</t>
+          <t>2343-132-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12388,28 +12388,28 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1266670.51</v>
+        <v>45099.02</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2343-132-CM26</t>
+          <t>1078177-297-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12434,43 +12434,43 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>SECCIÓN COMPRAS IX ZONA</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>40493784.1</v>
+        <v>8329.07</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1078177-297-CM26</t>
+          <t>2432-252-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12495,43 +12495,43 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>7478555</v>
+        <v>7221.22</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1078078-1168-CM26</t>
+          <t>4451-232-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12556,43 +12556,43 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>FIRAMCO SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.942.697-1</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>844662</v>
+        <v>879.09</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2432-252-CM26</t>
+          <t>4964-27-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12617,43 +12617,43 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>6483834</v>
+        <v>667.13</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4451-232-CM26</t>
+          <t>744835-205-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12678,43 +12678,43 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.255.100-1</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>FIRAMCO SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.942.697-1</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>789327</v>
+        <v>2177.53</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4964-27-CM26</t>
+          <t>3776-217-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12765,17 +12765,17 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>599010.3</v>
+        <v>8930.110000000001</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>744835-205-CM26</t>
+          <t>1078078-1189-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.255.100-1</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,28 +12815,28 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1955170</v>
+        <v>170.13</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3776-217-CM26</t>
+          <t>2343-141-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12851,53 +12851,53 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>8018220</v>
+        <v>5296.04</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2698-95-CM26</t>
+          <t>3596-299-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12917,17 +12917,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12937,28 +12937,28 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3432685.9</v>
+        <v>3192.33</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2343-141-CM26</t>
+          <t>2698-95-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12983,43 +12983,43 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4755240</v>
+        <v>3823.07</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3596-299-CM26</t>
+          <t>4284-196-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13044,43 +13044,43 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2866353</v>
+        <v>1827.9</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4284-196-CM26</t>
+          <t>1078078-1192-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13105,43 +13105,43 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1641248</v>
+        <v>25253.05</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1078078-1192-CM26</t>
+          <t>1078078-1187-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -13181,28 +13181,28 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>22674362.34</v>
+        <v>550.9400000000001</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1078078-1187-CM26</t>
+          <t>1078078-1180-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -13242,28 +13242,28 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>494683</v>
+        <v>927.04</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1078078-1189-CM26</t>
+          <t>1078078-1184-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13303,28 +13303,28 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>152753.16</v>
+        <v>167.56</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1078078-1184-CM26</t>
+          <t>1078078-1182-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -13364,28 +13364,28 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>150454.08</v>
+        <v>8898.66</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1078078-1182-CM26</t>
+          <t>1078078-1181-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13425,28 +13425,28 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>7989983.68</v>
+        <v>8005.01</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1078078-1181-CM26</t>
+          <t>1078078-1179-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13486,28 +13486,28 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>7187588.1</v>
+        <v>581.72</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1078078-1180-CM26</t>
+          <t>1078078-1178-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -13547,28 +13547,28 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>832377.63</v>
+        <v>8416.719999999999</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1078078-1179-CM26</t>
+          <t>1078078-1186-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -13608,28 +13608,28 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>522321.94</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1078078-1178-CM26</t>
+          <t>1078078-1205-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13680,17 +13680,17 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>7557254.46</v>
+        <v>550.9400000000001</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1078078-1186-CM26</t>
+          <t>1078078-1204-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -13741,17 +13741,17 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1078078-1200-CM26</t>
+          <t>1078078-1203-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -13791,28 +13791,28 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7126297.15</v>
+        <v>1373.46</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1078078-1205-CM26</t>
+          <t>1078078-1202-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -13852,28 +13852,28 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>494683</v>
+        <v>648.91</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1078078-1203-CM26</t>
+          <t>1078078-1201-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13913,28 +13913,28 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1233214.85</v>
+        <v>8417.68</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1078078-1202-CM26</t>
+          <t>1078078-1200-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -13974,28 +13974,28 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>582650.1800000001</v>
+        <v>7936.75</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1078078-1201-CM26</t>
+          <t>1078078-1198-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -14035,28 +14035,28 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>7558120.78</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1078078-1199-CM26</t>
+          <t>1078078-1197-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14107,17 +14107,17 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>462605.36</v>
+        <v>315.56</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1078078-1204-CM26</t>
+          <t>1078078-1196-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14157,28 +14157,28 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8005.01</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1078078-1197-CM26</t>
+          <t>1078078-1195-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14229,17 +14229,17 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>283340.19</v>
+        <v>3105.25</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1078078-1196-CM26</t>
+          <t>1078078-1194-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -14279,28 +14279,28 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>7187588.1</v>
+        <v>11897.91</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1078078-1195-CM26</t>
+          <t>1078078-1199-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14351,17 +14351,17 @@
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2788158.1</v>
+        <v>515.22</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1078078-1194-CM26</t>
+          <t>2343-149-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14401,28 +14401,28 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>10682966.77</v>
+        <v>7573.19</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>4451-236-CM26</t>
+          <t>1078078-1211-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14437,53 +14437,53 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>ALEJANDRO IGLESIAS SOTO</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>8.751.811-6</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1523200</v>
+        <v>14185.06</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2817-224-CM26</t>
+          <t>1078078-1228-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14498,53 +14498,53 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>435632.82</v>
+        <v>8416.719999999999</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1078078-1198-CM26</t>
+          <t>1078078-1229-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -14595,17 +14595,17 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>7737028.95</v>
+        <v>1126.82</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2343-149-CM26</t>
+          <t>1078078-1230-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14620,22 +14620,22 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14645,28 +14645,28 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>6799862.3</v>
+        <v>7936.75</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1078078-1211-CM26</t>
+          <t>1078078-1231-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -14706,28 +14706,28 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>ALEJANDRO IGLESIAS SOTO</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>8.751.811-6</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>12736570</v>
+        <v>8416.719999999999</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1078078-1228-CM26</t>
+          <t>1078078-1234-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -14767,28 +14767,28 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>7557254.46</v>
+        <v>149.75</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1078078-1229-CM26</t>
+          <t>1078078-1233-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14828,28 +14828,28 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1011754.66</v>
+        <v>8016.84</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1078078-1230-CM26</t>
+          <t>1078078-1227-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -14889,28 +14889,28 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>7126297.15</v>
+        <v>336.29</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1078078-1231-CM26</t>
+          <t>1078078-1235-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -14950,28 +14950,28 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8485.309999999999</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1078078-1235-CM26</t>
+          <t>1078078-1236-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15011,28 +15011,28 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>7618841.72</v>
+        <v>1747.11</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1078078-1233-CM26</t>
+          <t>1078078-1232-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15072,28 +15072,28 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>7198211.23</v>
+        <v>593.24</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1078078-1234-CM26</t>
+          <t>1078078-1226-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -15133,28 +15133,28 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>134462.86</v>
+        <v>8016.84</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1078078-1227-CM26</t>
+          <t>1078078-1223-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -15194,28 +15194,28 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>301945.84</v>
+        <v>8616.940000000001</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1078078-1236-CM26</t>
+          <t>1078078-1224-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -15255,28 +15255,28 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1568704.41</v>
+        <v>745.83</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1078078-1232-CM26</t>
+          <t>1078078-1222-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -15316,28 +15316,28 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>532659.47</v>
+        <v>773.47</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1078078-1226-CM26</t>
+          <t>1078078-1221-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -15377,28 +15377,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>7198211.23</v>
+        <v>8485.309999999999</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1078078-1223-CM26</t>
+          <t>1078078-1220-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -15438,28 +15438,28 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>7737028.95</v>
+        <v>1261.78</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1078078-1224-CM26</t>
+          <t>1078078-1219-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -15499,28 +15499,28 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>669668.9300000001</v>
+        <v>2702.1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1078078-1222-CM26</t>
+          <t>1078078-1216-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15560,28 +15560,28 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>694489.95</v>
+        <v>59.44</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1078078-1221-CM26</t>
+          <t>1078078-1215-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15621,28 +15621,28 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>7618841.72</v>
+        <v>779.89</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1078078-1220-CM26</t>
+          <t>1078078-1214-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15682,28 +15682,28 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1132938.31</v>
+        <v>8485.309999999999</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1078078-1219-CM26</t>
+          <t>1057461-600-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15728,43 +15728,43 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2426177.95</v>
+        <v>130.7</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1078078-1216-CM26</t>
+          <t>1078078-1225-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15804,28 +15804,28 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>53372.69</v>
+        <v>1307.74</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1078078-1215-CM26</t>
+          <t>2981-514-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15865,28 +15865,28 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>700253.12</v>
+        <v>4636.68</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1078078-1214-CM26</t>
+          <t>1078078-1240-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -15926,28 +15926,28 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>7618841.72</v>
+        <v>1196.72</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1057461-600-CM26</t>
+          <t>1078078-1239-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15962,53 +15962,53 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>117351.85</v>
+        <v>8468.92</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1078078-1225-CM26</t>
+          <t>1078078-1241-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16059,17 +16059,17 @@
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1174200.37</v>
+        <v>575.6799999999999</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1078078-1240-CM26</t>
+          <t>1078078-1237-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -16109,28 +16109,28 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1074517.64</v>
+        <v>8016.84</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1078078-1242-CM26</t>
+          <t>1554-748-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16150,48 +16150,48 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>3245879.7</v>
+        <v>1311.42</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1078078-1241-CM26</t>
+          <t>1285502-10-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16216,43 +16216,43 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>516895.54</v>
+        <v>541</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2981-514-CM26</t>
+          <t>1078078-1238-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16277,12 +16277,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16292,22 +16292,22 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>4163215</v>
+        <v>851.92</v>
       </c>
     </row>
     <row r="261">
@@ -16364,377 +16364,11 @@
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>7618841.72</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>1078078-1238-CM26</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M262" s="2" t="n">
-        <v>764927.24</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>1078078-1237-CM26</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M263" s="2" t="n">
-        <v>7198211.23</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>1554-748-CM26</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>61.606.307-3</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M264" s="2" t="n">
-        <v>1177505</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>1285502-10-CM26</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>69.061.400-6</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M265" s="2" t="n">
-        <v>485758</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>1078078-1239-CM26</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>MIVIVIENDA SPA</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>76.897.437-3</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M266" s="2" t="n">
-        <v>7604124.99</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>1078078-1244-CM26</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>Cancelada</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>COMERCIAL ORIONIS SPA</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>77.721.492-6</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M267" s="2" t="n">
-        <v>746513.1800000001</v>
+        <v>8485.309999999999</v>
       </c>
     </row>
   </sheetData>
